--- a/tests/unit/fixtures/site-sheet-openpyxl.xlsx
+++ b/tests/unit/fixtures/site-sheet-openpyxl.xlsx
@@ -629,12 +629,12 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Vi er flere enn 100, eller flere selskaper?</t>
+          <t>Hva om vi er over 100 ansatte eller flere selskaper?</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>We are more than 100, or several companies?</t>
+          <t>What if we have over 100 employees, or several companies?</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
@@ -647,12 +647,12 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Da gjelder Flere selskaper, etter avtale. [Skriv til oss](/kontakt), så finner vi en løsning.</t>
+          <t>Da gjelder pakken Flere selskaper, med pris etter avtale. [Skriv til oss](/kontakt), så blir vi enige om en pris.</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Then Several companies applies, by agreement. [Write to us](/kontakt) and we will find a solution.</t>
+          <t>Then the Several companies plan applies, priced by agreement. [Write to us](/kontakt) and we will agree a price.</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr"/>
@@ -701,12 +701,12 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Én pris i måneden, alt inkludert</t>
+          <t>Kartlegg arbeidsmiljøet fra 265 kr i måneden</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>One price a month, everything included</t>
+          <t>Survey your work environment from NOK 265 a month</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr"/>
@@ -719,12 +719,12 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>Ingen tillegg for rapporter, integrasjoner eller antall målinger. Månedlig avtale uten bindingstid, og 15 dager gratis uten kortopplysninger.</t>
+          <t>Ingen tillegg for rapporter, integrasjoner eller flere målinger. Dere betaler per måned uten binding, og prøver gratis i 15 dager uten kort.</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>No add-ons for reports, integrations or number of surveys. A monthly agreement with no lock-in, and 15 days free without card details.</t>
+          <t>No add-ons for reports, integrations or extra surveys. You pay monthly with no lock-in, and try it free for 15 days without a card.</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr"/>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Dette får dere uansett pakke</t>
+          <t>Med i alle pakker</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>What you get on any plan</t>
+          <t>Included in every plan</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr"/>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Rapport som følger arbeidsmiljøloven § 3-1 bokstav c</t>
+          <t>Rapport klar til Arbeidstilsynet, etter arbeidsmiljøloven § 3-1 bokstav c</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>A report that follows section 3-1 letter c of the Working Environment Act</t>
+          <t>A report ready for the Labour Inspection Authority, under section 3-1 letter c of the Working Environment Act</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr"/>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Tilgang for verneombudet uten ekstra kostnad</t>
+          <t>Verneombudet er med uten ekstra kostnad</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>Access for the safety representative at no extra cost</t>
+          <t>The safety representative is included at no extra cost</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Alle priser er uten merverdiavgift. Pakken Vanlig legger til resultat per avdeling og team, anonyme samtaler med de ansatte og utvikling over tid.</t>
+          <t>Alle priser er eks. mva. Pakken Vanlig legger til resultat per avdeling og team, anonyme samtaler med de ansatte og utvikling over tid.</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">

--- a/tests/unit/fixtures/site-sheet-openpyxl.xlsx
+++ b/tests/unit/fixtures/site-sheet-openpyxl.xlsx
@@ -755,12 +755,12 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>Start gratis</t>
+          <t>Prøv gratis</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>Start free</t>
+          <t>Try it free</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>Ingen avdeling vises før minst fem har svart.</t>
+          <t>Ingen avdeling vises før minst 5 har svart.</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>No department is shown until at least five have answered.</t>
+          <t>No department is shown until at least 5 have answered.</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr"/>
@@ -935,12 +935,12 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Start gratis</t>
+          <t>Prøv gratis</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>Start free</t>
+          <t>Try it free</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr"/>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Start gratis</t>
+          <t>Prøv gratis</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>Start free</t>
+          <t>Try it free</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr"/>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Skriv inn organisasjonsnummeret, så henter vi resten fra Brønnøysundregistrene. Dere er i gang på tre minutter, og trenger ikke oppgi kort før dere har bestemt dere.</t>
+          <t>Skriv inn organisasjonsnummeret, så henter vi resten fra Brønnøysundregistrene. Dere er i gang på 3 minutter, og trenger ikke oppgi kort før dere har bestemt dere.</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>Enter the organisation number and we fetch the rest from the Norwegian company register. You are up and running in three minutes, and do not need to give card details before you have decided.</t>
+          <t>Enter the organisation number and we fetch the rest from the Norwegian company register. You are up and running in 3 minutes, and do not need to give card details before you have decided.</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr"/>

--- a/tests/unit/fixtures/site-sheet-openpyxl.xlsx
+++ b/tests/unit/fixtures/site-sheet-openpyxl.xlsx
@@ -484,12 +484,12 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Liten 265 kr og Vanlig 565 kr i måneden eks. mva. Ingen tillegg, ingen oppstartsavgift og ingen binding. Prøv gratis i 15 dager uten kort.</t>
+          <t>Liten 265 kr og Vanlig 565 kr i måneden eks. mva. Ingen tillegg, ingen oppstartsavgift og ingen binding. Prøv gratis i 15 dager, uten betalingskort.</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>Small NOK 265 and Usual NOK 565 a month excl. VAT. No add-ons, no start-up fee and no lock-in. Try free for 15 days without a card. (corrected)
+          <t>Small NOK 265 and Usual NOK 565 a month excl. VAT. No add-ons, no start-up fee and no lock-in. Try free for 15 days, no card needed. (corrected)
 second line</t>
         </is>
       </c>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Priser</t>
+          <t>Pris</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -521,12 +521,12 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Må vi oppgi kort for å prøve?</t>
+          <t>Hva om vi bare er tolv personer?</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>Do we need a card to try it?</t>
+          <t>What if there are only twelve of us?</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
@@ -539,12 +539,12 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Nei. Dere registrerer med organisasjonsnummeret og kan bruke Orgpuls i 15 dager uten kortopplysninger.</t>
+          <t>Da får dere tall for hele virksomheten. En avdeling vises bare når minst 5 i den har svart. Er færre enn 5 med på å svare, vises ingen tall – da kunne ikke svarene vært anonyme.</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>No. You sign up with your organisation number and can use Orgpuls for 15 days without card details.</t>
+          <t>Then you get figures for the whole organisation. A department is shown only once at least 5 people in it have answered. If fewer than 5 answer, no figures are shown – the answers could not be anonymous then.</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
@@ -557,12 +557,12 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Er det bindingstid?</t>
+          <t>Er svarene virkelig anonyme?</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Is there a lock-in?</t>
+          <t>Are the answers really anonymous?</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -575,12 +575,12 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Nei. Avtalen er månedlig, uten bindingstid og uten oppstartsavgift.</t>
+          <t>Ja. Vi lagrer aldri navn, e-postadresse eller IP-adresse sammen med svaret – det finnes ingen kolonne som kunne holdt koblingen. Og ingen gruppe vises før minst 5 personer har svart.</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>No. The agreement is monthly, with no lock-in and no start-up fee.</t>
+          <t>Yes. We never store a name, e-mail address or IP address with the answer – there is no column that could hold the link. And no group is shown until at least 5 people have answered.</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -593,12 +593,12 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Koster det noe for verneombudet?</t>
+          <t>Hvor mye tid tar det for oss?</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>Does the safety representative cost extra?</t>
+          <t>How much time does it take us?</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Nei. Verneombudet har tilgang uten ekstra kostnad.</t>
+          <t>Oppsettet tar under en time første gang. Deretter planlegger årshjulet rundene selv. De ansatte bruker 4 minutter på den årlige kartleggingen og et par minutter på en puls.</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>No. The safety representative has access at no extra cost.</t>
+          <t>Setup takes under an hour the first time. After that, the year wheel plans the rounds for you. Employees spend 4 minutes on the annual survey and a couple of minutes on a pulse.</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -629,12 +629,12 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Hva om vi er over 100 ansatte eller flere selskaper?</t>
+          <t>Hva skjer når vi passerer 25 ansatte?</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>What if we have over 100 employees, or several companies?</t>
+          <t>What happens when we pass 25 employees?</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
@@ -647,12 +647,12 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Da gjelder pakken Flere selskaper, med pris etter avtale. [Skriv til oss](/kontakt), så blir vi enige om en pris.</t>
+          <t>Da gjelder Vanlig, prisen for 26 til 100 ansatte. Daglig leder bytter plan under Oppsett, og alt dere har målt og alle tiltak følger med.</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Then the Several companies plan applies, priced by agreement. [Write to us](/kontakt) and we will agree a price.</t>
+          <t>Then the Usual plan applies, the price for 26 to 100 employees. The managing director changes the plan under Setup, and everything you have measured and all your measures come with you.</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>Priser</t>
+          <t>Pris</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Kartlegg arbeidsmiljøet fra 265 kr i måneden</t>
+          <t>Fra 265 kr i måneden. Alt inkludert.</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Survey your work environment from NOK 265 a month</t>
+          <t>From NOK 265 a month. Everything included.</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr"/>
@@ -719,12 +719,12 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>Ingen tillegg for rapporter, integrasjoner eller flere målinger. Dere betaler per måned uten binding, og prøver gratis i 15 dager uten kort.</t>
+          <t>Én fast pris etter antall ansatte – ikke per bruker, ikke per måling. Ingen bindingstid. Verneombud og tillitsvalgte koster ikke ekstra. Gratis i 15 dager, uten betalingskort.</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>No add-ons for reports, integrations or extra surveys. You pay monthly with no lock-in, and try it free for 15 days without a card.</t>
+          <t>One fixed price by headcount – not per user, not per survey. No lock-in. Safety and union representatives cost nothing extra. Free for 15 days, no card needed.</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr"/>

--- a/tests/unit/fixtures/site-sheet-openpyxl.xlsx
+++ b/tests/unit/fixtures/site-sheet-openpyxl.xlsx
@@ -539,12 +539,12 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Da får dere tall for hele virksomheten. En avdeling vises bare når minst 5 i den har svart. Er færre enn 5 med på å svare, vises ingen tall – da kunne ikke svarene vært anonyme.</t>
+          <t>Da får dere tall for hele virksomheten. Som standard vises en avdeling når minst 5 i den har svart; færre teller med i helheten. For små team kan daglig leder senke grensen til 3, men 5 er sterkt anbefalt – jo færre svar, jo lettere er det å kjenne igjen hvem som sa hva.</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Then you get figures for the whole organisation. A department is shown only once at least 5 people in it have answered. If fewer than 5 answer, no figures are shown – the answers could not be anonymous then.</t>
+          <t>Then you get figures for the whole organisation. By default a department is shown once at least 5 people in it have answered; fewer count in the whole. For small teams the managing director can lower the limit to 3, but 5 is strongly recommended – the fewer the answers, the easier it is to recognise who said what.</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
@@ -575,12 +575,12 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Ja. Vi lagrer aldri navn, e-postadresse eller IP-adresse sammen med svaret – det finnes ingen kolonne som kunne holdt koblingen. Og ingen gruppe vises før minst 5 personer har svart.</t>
+          <t>Ja. Vi lagrer aldri navn, e-postadresse eller IP-adresse sammen med svaret – det finnes ingen kolonne som kunne holdt koblingen. Og som standard vises ingen gruppe før minst 5 personer har svart; grensen kan aldri settes under 3.</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>Yes. We never store a name, e-mail address or IP address with the answer – there is no column that could hold the link. And no group is shown until at least 5 people have answered.</t>
+          <t>Yes. We never store a name, e-mail address or IP address with the answer – there is no column that could hold the link. And by default no group is shown until at least 5 people have answered; the limit can never be set below 3.</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>Ingen avdeling vises før minst 5 har svart.</t>
+          <t>Som standard vises ingen avdeling før minst 5 har svart.</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>No department is shown until at least 5 have answered.</t>
+          <t>By default, no department is shown until at least 5 have answered.</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr"/>

--- a/tests/unit/fixtures/site-sheet-openpyxl.xlsx
+++ b/tests/unit/fixtures/site-sheet-openpyxl.xlsx
@@ -466,12 +466,12 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Priser: medarbeiderundersøkelse fra 265 kr/mnd | Orgpuls</t>
+          <t>Priser: gratis å starte, fra 265 kr/mnd | Orgpuls</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Pricing: employee surveys from NOK 265/month | Orgpuls</t>
+          <t>Pricing: free to start, from NOK 265/month | Orgpuls</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
@@ -484,12 +484,12 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Liten 265 kr og Vanlig 565 kr i måneden eks. mva. Ingen tillegg, ingen oppstartsavgift og ingen binding. Prøv gratis i 15 dager, uten betalingskort.</t>
+          <t>Gratis for hovedkartleggingen. Liten 265 kr og Vanlig 565 kr i måneden eks. mva., to måneder gratis med årlig avtale. 15 dager med alt, uten kort.</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>Small NOK 265 and Usual NOK 565 a month excl. VAT. No add-ons, no start-up fee and no lock-in. Try free for 15 days, no card needed. (corrected)
+          <t>Free for the main survey. Small NOK 265 and Usual NOK 565 a month excl. VAT, two months free with a yearly agreement. 15 days with everything, no card. (corrected)
 second line</t>
         </is>
       </c>
@@ -521,12 +521,12 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Hva om vi bare er tolv personer?</t>
+          <t>Finnes det en gratisversjon?</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>What if there are only twelve of us?</t>
+          <t>Is there a free version?</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr"/>
@@ -539,12 +539,12 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Da får dere tall for hele virksomheten. Som standard vises en avdeling når minst 5 i den har svart; færre teller med i helheten. For små team kan daglig leder senke grensen til 3, men 5 er sterkt anbefalt – jo færre svar, jo lettere er det å kjenne igjen hvem som sa hva.</t>
+          <t>Ja. De første 15 dagene har dere alt. Velger dere ingen plan, fortsetter dere gratis med standard hovedkartlegging, resultatene og tiltakene – så lenge dere vil, uansett hvor mange dere er. Puls, bransjemoduler, egne spørsmål, sammenligning med tidligere runder og rapporten til Arbeidstilsynet følger med Liten og Vanlig.</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Then you get figures for the whole organisation. By default a department is shown once at least 5 people in it have answered; fewer count in the whole. For small teams the managing director can lower the limit to 3, but 5 is strongly recommended – the fewer the answers, the easier it is to recognise who said what.</t>
+          <t>Yes. For the first 15 days you have everything. If you choose no plan, you carry on for free with the standard main survey, the results and the measures – for as long as you like, however many you are. Pulses, industry modules, your own questions, comparisons with earlier rounds and the report for the Labour Inspection Authority come with Small and Usual.</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
@@ -557,12 +557,12 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>Er svarene virkelig anonyme?</t>
+          <t>Hva koster en årlig avtale?</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Are the answers really anonymous?</t>
+          <t>What does a yearly agreement cost?</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -575,12 +575,12 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Ja. Vi lagrer aldri navn, e-postadresse eller IP-adresse sammen med svaret – det finnes ingen kolonne som kunne holdt koblingen. Og som standard vises ingen gruppe før minst 5 personer har svart; grensen kan aldri settes under 3.</t>
+          <t>Ti måneders pris for tolv: Liten 2 650 kr og Vanlig 5 650 kr i året eks. mva., fakturert for ett år om gangen. Månedlig avtale har ingen bindingstid.</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>Yes. We never store a name, e-mail address or IP address with the answer – there is no column that could hold the link. And by default no group is shown until at least 5 people have answered; the limit can never be set below 3.</t>
+          <t>Ten months' price for twelve: Small NOK 2,650 and Usual NOK 5,650 a year excl. VAT, invoiced a year at a time. A monthly agreement has no lock-in.</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -593,12 +593,12 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Hvor mye tid tar det for oss?</t>
+          <t>Hva om vi bare er tolv personer?</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>How much time does it take us?</t>
+          <t>What if there are only twelve of us?</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Oppsettet tar under en time første gang. Deretter planlegger årshjulet rundene selv. De ansatte bruker 4 minutter på den årlige kartleggingen og et par minutter på en puls.</t>
+          <t>Da får dere tall for hele virksomheten. Som standard vises en avdeling når minst 5 i den har svart; færre teller med i helheten. For små team kan daglig leder senke grensen til 3, men 5 er sterkt anbefalt – jo færre svar, jo lettere er det å kjenne igjen hvem som sa hva.</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>Setup takes under an hour the first time. After that, the year wheel plans the rounds for you. Employees spend 4 minutes on the annual survey and a couple of minutes on a pulse.</t>
+          <t>Then you get figures for the whole organisation. By default a department is shown once at least 5 people in it have answered; fewer count in the whole. For small teams the managing director can lower the limit to 3, but 5 is strongly recommended – the fewer the answers, the easier it is to recognise who said what.</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -629,12 +629,12 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Hva skjer når vi passerer 25 ansatte?</t>
+          <t>Er svarene virkelig anonyme?</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>What happens when we pass 25 employees?</t>
+          <t>Are the answers really anonymous?</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr"/>
@@ -647,12 +647,12 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Da gjelder Vanlig, prisen for 26 til 100 ansatte. Daglig leder bytter plan under Oppsett, og alt dere har målt og alle tiltak følger med.</t>
+          <t>Ja. Vi lagrer aldri navn, e-postadresse eller IP-adresse sammen med svaret – det finnes ingen kolonne som kunne holdt koblingen. Og som standard vises ingen gruppe før minst 5 personer har svart; grensen kan aldri settes under 3.</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Then the Usual plan applies, the price for 26 to 100 employees. The managing director changes the plan under Setup, and everything you have measured and all your measures come with you.</t>
+          <t>Yes. We never store a name, e-mail address or IP address with the answer – there is no column that could hold the link. And by default no group is shown until at least 5 people have answered; the limit can never be set below 3.</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr"/>
@@ -701,12 +701,12 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Fra 265 kr i måneden. Alt inkludert.</t>
+          <t>Gratis å starte. Alt inkludert fra 265 kr i måneden.</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>From NOK 265 a month. Everything included.</t>
+          <t>Free to start. Everything included from NOK 265 a month.</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr"/>
@@ -719,12 +719,12 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>Én fast pris etter antall ansatte – ikke per bruker, ikke per måling. Ingen bindingstid. Verneombud og tillitsvalgte koster ikke ekstra. Gratis i 15 dager, uten betalingskort.</t>
+          <t>Én fast pris etter antall ansatte – ikke per bruker, ikke per måling. Månedlig uten bindingstid, eller årlig med to måneder gratis. Verneombud og tillitsvalgte koster ikke ekstra. 15 dager med alt, deretter gratis for hovedkartleggingen.</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>One fixed price by headcount – not per user, not per survey. No lock-in. Safety and union representatives cost nothing extra. Free for 15 days, no card needed.</t>
+          <t>One fixed price by headcount – not per user, not per survey. Monthly with no lock-in, or yearly with two months free. Safety and union representatives cost nothing extra. 15 days with everything, then free for the main survey.</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr"/>

--- a/tests/unit/fixtures/site-sheet-openpyxl.xlsx
+++ b/tests/unit/fixtures/site-sheet-openpyxl.xlsx
@@ -466,12 +466,12 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Priser: gratis å starte, fra 265 kr/mnd | Orgpuls</t>
+          <t>Priser: gratis arbeidsmiljøundersøkelse | Orgpuls</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Pricing: free to start, from NOK 265/month | Orgpuls</t>
+          <t>Pricing: free work environment survey | Orgpuls</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
@@ -484,12 +484,12 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Gratis for hovedkartleggingen. Liten 265 kr og Vanlig 565 kr i måneden eks. mva., to måneder gratis med årlig avtale. 15 dager med alt, uten kort.</t>
+          <t>Gratis årlig arbeidsmiljøundersøkelse. Liten 265 kr og Vanlig 565 kr i måneden eks. mva., to måneder gratis med årlig avtale. 15 dager med alt, uten kort.</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>Free for the main survey. Small NOK 265 and Usual NOK 565 a month excl. VAT, two months free with a yearly agreement. 15 days with everything, no card. (corrected)
+          <t>Free yearly work environment survey. Small NOK 265 and Usual NOK 565 a month excl. VAT, two months free yearly. 15 days with everything, no card. (corrected)
 second line</t>
         </is>
       </c>
@@ -665,12 +665,12 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>Medarbeiderundersøkelse som kartlegger det psykososiale arbeidsmiljøet, gjør funnene om til tiltak og viser om de virker. 15 dager gratis.</t>
+          <t>Arbeidsmiljøundersøkelse for kartleggingen arbeidsmiljøloven krever: anonymt, med tiltak og rapport til Arbeidstilsynet. Gratis å starte.</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>An employee survey that maps the psychosocial working environment, turns the findings into measures and shows whether they work. 15 days free.</t>
+          <t>A work environment survey for the mapping Norwegian law requires: anonymous, with measures and a report for the Labour Inspection Authority. Free to start.</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr"/>

--- a/tests/unit/fixtures/site-sheet-openpyxl.xlsx
+++ b/tests/unit/fixtures/site-sheet-openpyxl.xlsx
@@ -737,12 +737,12 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>Organisasjonsnummer</t>
+          <t>Navn på virksomheten</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>Organisation number</t>
+          <t>Company name</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr"/>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Skriv inn organisasjonsnummeret, så henter vi resten fra Brønnøysundregistrene. Dere er i gang på 3 minutter, og trenger ikke oppgi kort før dere har bestemt dere.</t>
+          <t>Skriv inn navnet på virksomheten og e-postadressen din, så er dere i gang på 3 minutter, og trenger ikke oppgi kort før dere har bestemt dere.</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>Enter the organisation number and we fetch the rest from the Norwegian company register. You are up and running in 3 minutes, and do not need to give card details before you have decided.</t>
+          <t>Enter the company name and your e-mail address, and you are up and running in 3 minutes, without giving card details before you have decided.</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr"/>
